--- a/artfynd/A 48784-2019 artfynd.xlsx
+++ b/artfynd/A 48784-2019 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125221011</v>
+        <v>125221012</v>
       </c>
       <c r="B3" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>682575</v>
+        <v>682570</v>
       </c>
       <c r="R3" t="n">
-        <v>7157369</v>
+        <v>7157314</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125221012</v>
+        <v>125221011</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>682570</v>
+        <v>682575</v>
       </c>
       <c r="R4" t="n">
-        <v>7157314</v>
+        <v>7157369</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 48784-2019 artfynd.xlsx
+++ b/artfynd/A 48784-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125221010</v>
+        <v>125221011</v>
       </c>
       <c r="B2" t="n">
-        <v>82597</v>
+        <v>91030</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125221011</v>
+        <v>125221010</v>
       </c>
       <c r="B4" t="n">
-        <v>91030</v>
+        <v>82597</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">

--- a/artfynd/A 48784-2019 artfynd.xlsx
+++ b/artfynd/A 48784-2019 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125221012</v>
+        <v>125221010</v>
       </c>
       <c r="B3" t="n">
-        <v>78810</v>
+        <v>82597</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>682570</v>
+        <v>682575</v>
       </c>
       <c r="R3" t="n">
-        <v>7157314</v>
+        <v>7157369</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125221010</v>
+        <v>125221012</v>
       </c>
       <c r="B4" t="n">
-        <v>82597</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>682575</v>
+        <v>682570</v>
       </c>
       <c r="R4" t="n">
-        <v>7157369</v>
+        <v>7157314</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 48784-2019 artfynd.xlsx
+++ b/artfynd/A 48784-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125221011</v>
+        <v>125221012</v>
       </c>
       <c r="B2" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>682575</v>
+        <v>682570</v>
       </c>
       <c r="R2" t="n">
-        <v>7157369</v>
+        <v>7157314</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125221012</v>
+        <v>125221011</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>682570</v>
+        <v>682575</v>
       </c>
       <c r="R4" t="n">
-        <v>7157314</v>
+        <v>7157369</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 48784-2019 artfynd.xlsx
+++ b/artfynd/A 48784-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125221012</v>
+        <v>125221010</v>
       </c>
       <c r="B2" t="n">
-        <v>78810</v>
+        <v>82737</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>682570</v>
+        <v>682575</v>
       </c>
       <c r="R2" t="n">
-        <v>7157314</v>
+        <v>7157369</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125221010</v>
+        <v>125221012</v>
       </c>
       <c r="B3" t="n">
-        <v>82597</v>
+        <v>78947</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>682575</v>
+        <v>682570</v>
       </c>
       <c r="R3" t="n">
-        <v>7157369</v>
+        <v>7157314</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -890,7 +890,7 @@
         <v>125221011</v>
       </c>
       <c r="B4" t="n">
-        <v>91030</v>
+        <v>91184</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 48784-2019 artfynd.xlsx
+++ b/artfynd/A 48784-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125221010</v>
+        <v>125221011</v>
       </c>
       <c r="B2" t="n">
-        <v>82737</v>
+        <v>91184</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125221012</v>
+        <v>125221010</v>
       </c>
       <c r="B3" t="n">
-        <v>78947</v>
+        <v>82737</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>682570</v>
+        <v>682575</v>
       </c>
       <c r="R3" t="n">
-        <v>7157314</v>
+        <v>7157369</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125221011</v>
+        <v>125221012</v>
       </c>
       <c r="B4" t="n">
-        <v>91184</v>
+        <v>78947</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>682575</v>
+        <v>682570</v>
       </c>
       <c r="R4" t="n">
-        <v>7157369</v>
+        <v>7157314</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 48784-2019 artfynd.xlsx
+++ b/artfynd/A 48784-2019 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125221011</v>
+        <v>125221010</v>
       </c>
       <c r="B2" t="n">
-        <v>91184</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>82779</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -781,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125221010</v>
+        <v>125221011</v>
       </c>
       <c r="B3" t="n">
-        <v>82737</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91238</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -890,12 +880,7 @@
         <v>125221012</v>
       </c>
       <c r="B4" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 48784-2019 artfynd.xlsx
+++ b/artfynd/A 48784-2019 artfynd.xlsx
@@ -779,7 +779,7 @@
         <v>125221011</v>
       </c>
       <c r="B3" t="n">
-        <v>91238</v>
+        <v>91245</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
